--- a/my-world-cup/database/2_ability_models/Brazil/C组/巴西队.xlsx
+++ b/my-world-cup/database/2_ability_models/Brazil/C组/巴西队.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\AI_Coding\My_World_Cup\C组\巴西\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\AI_Coding\My_World_Cup\my-world-cup\database\2_ability_models\Brazil\C组\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF12AAD2-911F-40F3-AFC0-AA120449A285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1BCD1C-EA70-4AAC-B889-F5A7C400CFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="465" windowWidth="31905" windowHeight="20415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="216">
   <si>
     <t>字段</t>
   </si>
@@ -486,9 +486,6 @@
     <t>Estádio Nacional Mané Garrincha, Brasília (H)</t>
   </si>
   <si>
-    <t>哥伦比亚 Colombia</t>
-  </si>
-  <si>
     <t>2–1</t>
   </si>
   <si>
@@ -504,9 +501,6 @@
     <t>Estadio Monumental, Buenos Aires (A)</t>
   </si>
   <si>
-    <t>阿根廷 Argentina</t>
-  </si>
-  <si>
     <t>1–4</t>
   </si>
   <si>
@@ -516,9 +510,6 @@
     <t>Estadio Monumental Isidro Romero Carbo, Guayaquil (A)</t>
   </si>
   <si>
-    <t>厄瓜多尔 Ecuador</t>
-  </si>
-  <si>
     <t>0–0</t>
   </si>
   <si>
@@ -528,9 +519,6 @@
     <t>Neo Química Arena, São Paulo (H)</t>
   </si>
   <si>
-    <t>巴拉圭 Paraguay</t>
-  </si>
-  <si>
     <t>1–0</t>
   </si>
   <si>
@@ -540,9 +528,6 @@
     <t>Maracanã, Rio de Janeiro (H)</t>
   </si>
   <si>
-    <t>智利 Chile</t>
-  </si>
-  <si>
     <t>3–0</t>
   </si>
   <si>
@@ -552,9 +537,6 @@
     <t>El Alto Municipal Stadium, El Alto (A)</t>
   </si>
   <si>
-    <t>玻利维亚 Bolivia</t>
-  </si>
-  <si>
     <t>0–1</t>
   </si>
   <si>
@@ -564,9 +546,6 @@
     <t>Seoul World Cup Stadium, Seoul (A)</t>
   </si>
   <si>
-    <t>韩国 South Korea</t>
-  </si>
-  <si>
     <t>5–0</t>
   </si>
   <si>
@@ -579,9 +558,6 @@
     <t>Ajinomoto Stadium, Chōfu (A)</t>
   </si>
   <si>
-    <t>日本 Japan</t>
-  </si>
-  <si>
     <t>2–3</t>
   </si>
   <si>
@@ -591,9 +567,6 @@
     <t>Emirates Stadium, London (N)</t>
   </si>
   <si>
-    <t>塞内加尔 Senegal</t>
-  </si>
-  <si>
     <t>2–0</t>
   </si>
   <si>
@@ -603,9 +576,6 @@
     <t>Stade Pierre-Mauroy, Lille (N)</t>
   </si>
   <si>
-    <t>突尼斯 Tunisia</t>
-  </si>
-  <si>
     <t>1–1</t>
   </si>
   <si>
@@ -615,9 +585,6 @@
     <t>Gillette Stadium, Foxborough (N)</t>
   </si>
   <si>
-    <t>法国 France</t>
-  </si>
-  <si>
     <t>1–2</t>
   </si>
   <si>
@@ -627,18 +594,12 @@
     <t>Camping World Stadium, Orlando (N)</t>
   </si>
   <si>
-    <t>克罗地亚 Croatia</t>
-  </si>
-  <si>
     <t>3–1</t>
   </si>
   <si>
     <t>2026-05-31</t>
   </si>
   <si>
-    <t>巴拿马 Panama</t>
-  </si>
-  <si>
     <t>6–2</t>
   </si>
   <si>
@@ -648,21 +609,12 @@
     <t>Huntington Bank Field, Cleveland (N)</t>
   </si>
   <si>
-    <t>埃及 Egypt</t>
-  </si>
-  <si>
     <t>2026-06-13</t>
   </si>
   <si>
     <t>MetLife Stadium, East Rutherford (N)</t>
   </si>
   <si>
-    <t>摩洛哥 Morocco</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>2026年国际足联世界杯 2026 FIFA World Cup</t>
   </si>
   <si>
@@ -672,16 +624,72 @@
     <t>Lincoln Financial Field, Philadelphia (N)</t>
   </si>
   <si>
-    <t>海地 Haiti</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>Hard Rock Stadium, Miami Gardens (N)</t>
-  </si>
-  <si>
-    <t>苏格兰 Scotland</t>
+    <t>3–0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 海地 Haiti</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 摩洛哥 Morocco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 埃及 Egypt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 巴拿马 Panama</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 克罗地亚 Croatia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 法国 France</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 突尼斯 Tunisia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 塞内加尔 Senegal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 日本 Japan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 韩国 South Korea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 玻利维亚 Bolivia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 智利 Chile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 巴拉圭 Paraguay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 厄瓜多尔 Ecuador</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 阿根廷 Argentina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴西 vs 哥伦比亚 Colombia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2195,12 +2203,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352E195B-6E63-4545-BCD8-3F1844452045}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.875" customWidth="1"/>
     <col min="2" max="2" width="56.75" customWidth="1"/>
-    <col min="3" max="3" width="23.625" customWidth="1"/>
+    <col min="3" max="3" width="30.125" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
     <col min="5" max="5" width="59.25" customWidth="1"/>
     <col min="6" max="6" width="21.875" customWidth="1"/>
@@ -2234,336 +2242,316 @@
         <v>152</v>
       </c>
       <c r="C2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" t="s">
         <v>153</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>154</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>155</v>
-      </c>
-      <c r="F2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
         <v>157</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" t="s">
         <v>158</v>
       </c>
-      <c r="C3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" t="s">
-        <v>160</v>
-      </c>
       <c r="E3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" t="s">
         <v>155</v>
-      </c>
-      <c r="F3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" t="s">
         <v>161</v>
       </c>
-      <c r="B4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" t="s">
-        <v>164</v>
-      </c>
       <c r="E4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" t="s">
         <v>155</v>
-      </c>
-      <c r="F4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" t="s">
         <v>155</v>
-      </c>
-      <c r="F5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" t="s">
         <v>155</v>
-      </c>
-      <c r="F6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" t="s">
         <v>155</v>
-      </c>
-      <c r="F7" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D12" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>203</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="F17" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B18" t="s">
-        <v>217</v>
-      </c>
-      <c r="C18" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" t="s">
-        <v>211</v>
-      </c>
-      <c r="E18" t="s">
-        <v>212</v>
-      </c>
-      <c r="F18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
